--- a/template_import_khach_hang.xlsx
+++ b/template_import_khach_hang.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -407,6 +407,8 @@
     <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,6 +433,12 @@
       <c r="G1" t="str">
         <v>Buổi còn lại</v>
       </c>
+      <c r="H1" t="str">
+        <v>Ngày bắt đầu</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Ngày kết thúc</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -454,6 +462,12 @@
       <c r="G2">
         <v>10</v>
       </c>
+      <c r="H2" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-07-15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -477,21 +491,27 @@
       <c r="G3">
         <v>12</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="65.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,9 +602,31 @@
         <v>Số buổi còn lại hiện tại. Để trống = bằng tổng buổi ĐK</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Ngày bắt đầu</v>
+      </c>
+      <c r="B9" t="str">
+        <v>⚠️ Tùy chọn</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Ngày bắt đầu hiệu lực gói. Định dạng: YYYY-MM-DD (VD: 2026-01-15). Để trống = chưa kích hoạt</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Ngày kết thúc</v>
+      </c>
+      <c r="B10" t="str">
+        <v>⚠️ Tùy chọn</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Ngày hết hạn gói. Định dạng: YYYY-MM-DD. Để trống = không giới hạn</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>